--- a/config/generated/templates/EnemyStat.xlsx
+++ b/config/generated/templates/EnemyStat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
   <si>
     <t>@table</t>
   </si>
@@ -40,7 +40,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>ce44b75f1366ea03</t>
+    <t>7371b7efcb839c1c</t>
   </si>
   <si>
     <t>#name</t>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>spd_decimal</t>
+  </si>
+  <si>
+    <t>effect_hit_rate_decimal</t>
   </si>
   <si>
     <t>effect_resistance_decimal</t>
@@ -520,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -528,11 +531,12 @@
     <col min="3" max="3" width="12.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="5" customWidth="1"/>
     <col min="5" max="8" width="12.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1">
+    <row r="2" spans="1:11" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -593,10 +597,13 @@
       <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -625,42 +632,48 @@
       <c r="J3" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="K3" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -689,40 +702,46 @@
       <c r="J5" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="K5" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="42" customHeight="1">
+    <row r="7" spans="1:11" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -733,6 +752,7 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/config/generated/templates/EnemyStat.xlsx
+++ b/config/generated/templates/EnemyStat.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>7371b7efcb839c1c</t>
+    <t>4b43612aa8e4f1f4</t>
   </si>
   <si>
     <t>#name</t>
@@ -91,7 +91,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
